--- a/docs/tong-hop-yeu-cau-2026-08-22.xlsx
+++ b/docs/tong-hop-yeu-cau-2026-08-22.xlsx
@@ -15,9 +15,14 @@
     <sheet name="005" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="006" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="007" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="008" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="009" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="010" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="011" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="012" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng quan'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng quan'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'001'!$A$2:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'002'!$A$2:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'003'!$A$2:$E$18</definedName>
@@ -25,6 +30,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'005'!$A$2:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'006'!$A$2:$E$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'007'!$A$2:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'008'!$A$2:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'009'!$A$2:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'010'!$A$2:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'011'!$A$2:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'012'!$A$2:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -743,36 +753,3362 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>008-versioned-event-schemas</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Schema sự kiện có đánh phiên bản — OrderPlaced, BasketCheckedOut</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú phương pháp tổng hợp</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>009-retrofit-tdd-basket-order</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Bổ sung ngược TDD cho tính giá giỏ hàng và tạo đơn hàng</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Toàn bộ nội dung được trích từ specs/*/spec.md rồi dịch sang tiếng Việt; không suy luận, không bổ sung.</t>
+          <t>010-testcontainers-integration-tests</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Hạ tầng kiểm thử tích hợp bằng Testcontainers</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>010</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Một FR chỉ được nối với Kịch bản chấp nhận / Kết quả đo lường được khi trong spec có tham chiếu tường minh (nhắc đích danh mã FR-xxx hoặc SC-xxx).</t>
+          <t>011-consumer-contract-tests</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm thử hợp đồng do bên tiêu thụ dẫn dắt trên các ranh giới BFF/service</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>011</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>012-sonarqube-quality-gate</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cổng chất lượng SonarQube làm rào chặn merge</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú phương pháp tổng hợp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Toàn bộ nội dung được trích từ specs/*/spec.md rồi dịch sang tiếng Việt; không suy luận, không bổ sung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Một FR chỉ được nối với Kịch bản chấp nhận / Kết quả đo lường được khi trong spec có tham chiếu tường minh (nhắc đích danh mã FR-xxx hoặc SC-xxx).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>FR không có tham chiếu tường minh nào được đánh dấu "Chưa có liên kết tường minh trong spec"; các mục còn lại nằm ở hai khối cuối mỗi sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>009-retrofit-tdd-basket-order — Bổ sung ngược TDD cho tính giá giỏ hàng và tạo đơn hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Logic tính giá giỏ hàng PHẢI từ chối việc thêm một dòng hàng có số lượng nhỏ hơn một.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:71</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>100% các quy tắc tính giá giỏ hàng và tạo đơn hàng được nêu tên trong đặc tả này (FR-001 đến FR-006) đều có một bài kiểm thử tự động đang chạy đạt, và bài kiểm thử đó thất bại khi quy tắc bị hoàn tác.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:91</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Logic tính giá giỏ hàng PHẢI giữ lại đơn giá ban đầu của một dòng hàng khi cùng sản phẩm đó được thêm lại, kể cả khi giá cung cấp ở lần thêm sau khác đi.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:72</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Logic tính giá giỏ hàng PHẢI gộp lần thêm lặp lại của cùng một sản phẩm vào số lượng của dòng hàng đã có, thay vì tạo ra dòng thứ hai cho sản phẩm đó.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:73</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Logic tạo đơn hàng PHẢI từ chối việc đặt một đơn hàng không có dòng hàng nào.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:74</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Logic tạo đơn hàng PHẢI từ chối việc đặt một đơn hàng có chứa dòng hàng với số lượng nhỏ hơn một hoặc đơn giá âm.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:75</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Logic tạo đơn hàng PHẢI tự tính tổng tiền của đơn hàng từ các dòng hàng của nó, thay vì chấp nhận tổng tiền do bên gọi cung cấp.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:76</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>100% các quy tắc tính giá giỏ hàng và tạo đơn hàng được nêu tên trong đặc tả này (FR-001 đến FR-006) đều có một bài kiểm thử tự động đang chạy đạt, và bài kiểm thử đó thất bại khi quy tắc bị hoàn tác.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:91</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Mỗi yêu cầu từ FR-001 đến FR-006 PHẢI được chứng minh bằng một unit test thất bại khi quy tắc tương ứng bị gỡ bỏ hoặc bị làm suy yếu.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:77</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Mọi commit đưa vào hoặc thay đổi logic tính giá giỏ hàng hay tạo đơn hàng trong đợt làm này PHẢI có, trong lịch sử commit, một commit test đi trước hoặc đi kèm — commit test đó thất bại khi chưa có thay đổi và thành công khi đã có thay đổi.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:78</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện giỏ hàng chưa có dòng nào cho một sản phẩm, Khi thêm một dòng hàng với số lượng bằng không (hoặc âm), Thì lần thêm đó bị từ chối và có một unit test khẳng định việc từ chối này.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB2</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện giỏ hàng đã có một dòng cho một sản phẩm với đơn giá ban đầu của nó, Khi cùng sản phẩm đó được thêm lại sau khi giá trong danh mục đã thay đổi, Thì đơn giá của dòng hàng đã có được giữ nguyên và có một unit test khẳng định giá ban đầu được bảo toàn.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB3</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện giỏ hàng đã có một dòng cho một sản phẩm, Khi cùng sản phẩm đó được thêm lại với số lượng khác, Thì số lượng của dòng hàng đã có tăng thêm đúng lượng mới thay vì tạo ra dòng thứ hai, và có một unit test khẳng định không tồn tại dòng trùng lặp.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện không có dòng hàng nào, Khi đặt một đơn hàng ở tầng miền nghiệp vụ (domain layer), Thì nỗ lực đó bị từ chối và có một unit test khẳng định việc từ chối này.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB2</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện có một hoặc nhiều dòng hàng hợp lệ, Khi đặt một đơn hàng, Thì tổng tiền của đơn hàng thu được bằng tổng của tích số lượng nhân đơn giá từng dòng, do logic tạo đơn hàng tự tính chứ không phải do bên gọi cung cấp, và có một unit test khẳng định điều này.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB3</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện có một dòng hàng với số lượng không hợp lệ hoặc đơn giá âm, Khi đặt một đơn hàng, Thì nỗ lực đó bị từ chối và có một unit test khẳng định việc từ chối này.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện xét lịch sử commit của đợt làm này, Khi người soát xét kiểm tra từng commit có động tới logic tính giá giỏ hàng hoặc tạo đơn hàng, Thì mọi commit như vậy đều có một commit test thất bại đi trước hoặc đi kèm.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SC-002</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>100% các commit động tới logic tính giá giỏ hàng hoặc tạo đơn hàng trong đợt làm này đều cho thấy một thay đổi về test được đưa vào cùng lúc hoặc trước thay đổi hiện thực, xác nhận được chỉ bằng một lượt rà lịch sử commit.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:92</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SC-003</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Nỗ lực đặt đơn hàng từ một giỏ hàng rỗng bị từ chối ở 100% số trường hợp và chứng minh được là đã có kiểm thử tự động bao phủ, không cần bước kiểm chứng thủ công nào.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:93</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SC-004</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Bộ kiểm thử tự động cho phần tính giá giỏ hàng và tạo đơn hàng sẽ thất bại ngay lập tức nếu hành vi trước khi bổ sung ngược của Phase 1 (thiếu chặn số lượng tối thiểu, thiếu quy tắc ổn định giá, hoặc chấp nhận đơn hàng từ giỏ rỗng) bị đưa trở lại.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>specs/009-retrofit-tdd-basket-order/spec.md:94</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E18"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A29:E29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>010-testcontainers-integration-tests — Hạ tầng kiểm thử tích hợp bằng Testcontainers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Các bộ kiểm thử tích hợp của baskets, orders, parties và products PHẢI tiếp tục chạy trên một container SQL Server thật thông qua Testcontainers, chứ không dùng provider chạy trong bộ nhớ hay provider giả lập.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:111</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Với mỗi service được rà soát, PHẢI chứng minh được có ít nhất một bài kiểm thử tích hợp thất bại khi một ràng buộc SQL thật mà nó phụ thuộc bị gỡ bỏ, và đạt trở lại khi ràng buộc được khôi phục — qua đó chứng minh bài kiểm thử thực sự chạy trên engine thật.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:114</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có một fixture Redis dùng lại được cho Testcontainers, để bất kỳ project kiểm thử nào cũng dùng được nó nhằm khởi động một container Redis thật và lấy được thông tin kết nối tới container đó.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:117</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có một fixture RabbitMQ dùng lại được cho Testcontainers, để bất kỳ project kiểm thử nào cũng dùng được nó nhằm khởi động một container RabbitMQ thật và lấy được thông tin kết nối tới container đó.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có ít nhất một bài kiểm thử chứng minh fixture Redis kết nối tới được (thực hiện một thao tác đọc/ghi thật trên container đã khởi động).</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:121</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có ít nhất một bài kiểm thử chứng minh fixture RabbitMQ kết nối tới được (thực hiện một kết nối thật tới container đã khởi động).</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:123</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Khi bất kỳ container nào trong ba container (SQL Server, Redis, RabbitMQ) không đạt trạng thái khỏe mạnh trong lúc khởi động fixture, lượt chạy kiểm thử PHẢI thất bại kèm thông báo lỗi chỉ rõ container nào hỏng, thay vì âm thầm bỏ qua các bài kiểm thử phụ thuộc.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:125</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có ít nhất một bài kiểm thử chứng minh rằng việc giết container RabbitMQ giữa chừng khiến bài kiểm thử bị ảnh hưởng thất bại trong một khoảng thời gian có giới hạn, thay vì treo vô thời hạn.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:128</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>FR-009</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Feature này KHÔNG ĐƯỢC đưa vào hành vi caching hay messaging mới ở môi trường chạy thật — không mã nguồn runtime của service nào bắt đầu phụ thuộc vào Redis hay RabbitMQ vì feature này. Chỉ bổ sung hạ tầng phục vụ kiểm thử.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:130</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện bộ kiểm thử tích hợp của một service được rà soát đang chạy, Khi nó khởi động, Thì một container SQL Server thật nhìn thấy được trong docker ps trong suốt thời gian chạy.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện chủ ý đưa vào một vi phạm ràng buộc SQL thật, Khi bộ kiểm thử tích hợp chạy, Thì bài kiểm thử liên quan thất bại vì engine thật đã từ chối thao tác, và đạt trở lại khi vi phạm được hoàn tác.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện container SQL Server không đạt trạng thái khỏe mạnh lúc khởi động, Khi bộ kiểm thử chạy, Thì lượt chạy thất bại kèm thông báo lỗi rõ ràng chỉ đích danh container đó, thay vì âm thầm bỏ qua các bài kiểm thử bị ảnh hưởng.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một project kiểm thử tham chiếu tới fixture Redis, Khi bộ kiểm thử khởi động, Thì một container Redis thật được khởi động và kết nối tới được bằng thông tin kết nối mà fixture cung cấp.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB2</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện container Redis không đạt trạng thái khỏe mạnh lúc khởi động, Khi bộ kiểm thử chạy, Thì lượt chạy thất bại kèm thông báo lỗi rõ ràng chỉ đích danh container đó, thay vì âm thầm bỏ qua các bài kiểm thử bị ảnh hưởng.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một project kiểm thử tham chiếu tới fixture RabbitMQ, Khi bộ kiểm thử khởi động, Thì một container RabbitMQ thật được khởi động và kết nối tới được bằng thông tin kết nối mà fixture cung cấp.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB2</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện container RabbitMQ không đạt trạng thái khỏe mạnh lúc khởi động, Khi bộ kiểm thử chạy, Thì lượt chạy thất bại kèm thông báo lỗi rõ ràng chỉ đích danh container đó, thay vì âm thầm bỏ qua các bài kiểm thử bị ảnh hưởng.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:87</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB3</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một bài kiểm thử đang kết nối tới container RabbitMQ đang chạy, Khi container bị giết giữa chừng, Thì bài kiểm thử thất bại trong khoảng thời gian có giới hạn thay vì treo vô thời hạn.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:90</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>QA có thể chạy trọn bộ kiểm thử tích hợp ở máy cục bộ và quan sát thấy cả ba container SQL Server, Redis và RabbitMQ đều hiện diện trong docker ps trong suốt lượt chạy.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:138</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SC-002</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Một vi phạm ràng buộc SQL được chủ ý đưa vào đều bị một bài kiểm thử tích hợp bắt được 100% số lần đưa vào, trên mọi service được rà soát.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:140</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SC-003</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Nếu bất kỳ container nào trong ba container không đạt trạng thái khỏe mạnh, lượt chạy bộ kiểm thử thất bại và báo tên container bị hỏng — không có trường hợp nào âm thầm bỏ qua.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:142</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SC-004</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Một container RabbitMQ bị giết giữa chừng khiến bài kiểm thử bị ảnh hưởng thất bại trong vòng 30 giây thay vì treo vô thời hạn.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:144</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SC-005</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Một feature trong tương lai bổ sung caching bằng Redis hay phát sự kiện qua RabbitMQ cho một service có thể dùng lại fixture Redis hoặc RabbitMQ của feature này mà không phải sửa đổi chúng.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>specs/010-testcontainers-integration-tests/spec.md:146</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E20"/>
+  <mergeCells count="3">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>011-consumer-contract-tests — Kiểm thử hợp đồng do bên tiêu thụ dẫn dắt trên các ranh giới BFF/service</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Service products PHẢI kiểm chứng các response HTTP thật của nó gửi cho BFF so với những kỳ vọng đã được ghi thành tài liệu của BFF với tư cách bên tiêu thụ, ngay trong chính build của service products.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Service baskets PHẢI kiểm chứng các response HTTP thật của nó gửi cho BFF so với những kỳ vọng đã được ghi thành tài liệu của BFF với tư cách bên tiêu thụ, ngay trong chính build của service baskets.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Service orders PHẢI kiểm chứng các response HTTP thật của nó gửi cho BFF so với những kỳ vọng đã được ghi thành tài liệu của BFF với tư cách bên tiêu thụ, ngay trong chính build của service orders.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Service phát hành sự kiện tích hợp được chọn thí điểm PHẢI kiểm chứng nội dung sự kiện (payload) mà nó dựng ra so với những kỳ vọng đã được ghi thành tài liệu của service tiêu thụ, ngay trong chính build của service phát hành.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:121</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Khi response thật của một bên sản xuất (hoặc payload sự kiện của một bên phát hành) lệch khỏi kỳ vọng đã ghi trong tài liệu của bên tiêu thụ, chính build của bên sản xuất (hoặc bên phát hành) PHẢI thất bại — lỗi này KHÔNG ĐƯỢC chỉ lộ ra ở build của bên tiêu thụ phía sau hoặc muộn hơn.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:124</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Việc kiểm chứng hợp đồng PHẢI chạy trên hành vi thật của bên sản xuất (một response HTTP thật, hoặc một payload sự kiện thật được dựng ra), chứ không phải trên một bản thay thế do người duy trì thủ công.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:127</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Một trường được thêm vào mà bên tiêu thụ không dùng đến KHÔNG ĐƯỢC làm bài kiểm thử hợp đồng thất bại, nhất quán với quy tắc tolerant reader của nền tảng.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Toàn bộ tập ranh giới HTTP và ranh giới sự kiện trong lát cắt mỏng (BFF↔products, BFF↔baskets, BFF↔orders, và cặp bên sản xuất↔bên tiêu thụ của sự kiện thí điểm) PHẢI liệt kê được và đối chiếu chéo được với tập các bài kiểm thử hợp đồng hiện có.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:132</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>FR-009</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Một ranh giới trong lát cắt mỏng còn thiếu bài kiểm thử hợp đồng bắt buộc PHẢI phát hiện được — bằng một bước kiểm tra độ bao phủ tự động ở nơi đã có, hoặc được ghi thành mục rà soát thủ công ở nơi chưa có.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:135</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện đã có tài liệu ghi kỳ vọng của BFF đối với response của service products, Khi chính build của service products chạy, Thì nó kiểm chứng các response thật của mình so với những kỳ vọng đó và làm hỏng build nếu có sai lệch.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện đã có tài liệu ghi kỳ vọng của BFF đối với response của service baskets, Khi chính build của service baskets chạy, Thì nó kiểm chứng các response thật của mình so với những kỳ vọng đó và làm hỏng build nếu có sai lệch.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện đã có tài liệu ghi kỳ vọng của BFF đối với response của service orders, Khi chính build của service orders chạy, Thì nó kiểm chứng các response thật của mình so với những kỳ vọng đó và làm hỏng build nếu có sai lệch.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB4</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một bên sản xuất thay đổi hình dạng response theo kiểu phá vỡ tương thích, Khi build của nó chạy, Thì bài kiểm thử hợp đồng thất bại trước khi thay đổi kịp được merge.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện đã có tài liệu ghi kỳ vọng của một service tiêu thụ đối với một sự kiện tích hợp được phát hành, Khi chính build của service phát hành chạy, Thì nó kiểm chứng payload sự kiện mà nó sẽ phát ra so với những kỳ vọng đó và làm hỏng build nếu có sai lệch.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:64</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB2</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một service phát hành thay đổi hình dạng của một sự kiện theo kiểu phá vỡ tương thích, Khi build của nó chạy, Thì bài kiểm thử hợp đồng thất bại trước khi thay đổi kịp được merge.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:67</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện xét bốn ranh giới trong lát cắt mỏng (BFF↔products, BFF↔baskets, BFF↔orders, và cặp bên sản xuất↔bên tiêu thụ của sự kiện thí điểm), Khi có người liệt kê chúng ra, Thì mỗi ranh giới đều có một bài kiểm thử hợp đồng tương ứng, tìm được mà không cần đọc phần bên trong của service.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:87</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một bài kiểm thử hợp đồng bắt buộc bị gỡ bỏ, Khi bước kiểm tra độ bao phủ chạy (cổng kiểm soát tự động) hoặc khi người soát xét thực hiện bước kiểm tra thủ công tương đương (nếu chưa có cổng tự động), Thì lỗ hổng đó bị phát hiện trước khi merge.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:90</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>100% bốn ranh giới trong lát cắt mỏng (BFF↔products, BFF↔baskets, BFF↔orders, và cặp bên sản xuất↔bên tiêu thụ của sự kiện thí điểm) đều có một bài kiểm thử hợp đồng đi kèm.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:153</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SC-002</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Khi hình dạng dữ liệu của một bên sản xuất hoặc bên phát hành phá vỡ một kỳ vọng đã ghi trong tài liệu của bên tiêu thụ, chính build của bên sản xuất hoặc bên phát hành đó thất bại ngay trong cùng lượt build, ở 100% số trường hợp đã kiểm thử trên cả bốn ranh giới — không bao giờ chỉ thất bại ở build của bên tiêu thụ phía sau.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:155</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SC-003</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Người soát xét có thể xác định ranh giới nào trong bốn ranh giới của lát cắt mỏng đã có kiểm thử hợp đồng bao phủ trong dưới 5 phút, chỉ dựa vào bản kiểm kê các bài kiểm thử hợp đồng, không phải đọc mã nguồn của service.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:158</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SC-004</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Việc gỡ bỏ một bài kiểm thử hợp đồng bắt buộc của một ranh giới đã được bao phủ đều bị phát hiện trước khi merge — hoặc do một cổng kiểm soát tự động báo lỗi, hoặc do một bước rà soát thủ công đã ghi trong tài liệu — ở 100% số trường hợp.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>specs/011-consumer-contract-tests/spec.md:161</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E20"/>
+  <mergeCells count="3">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>012-sonarqube-quality-gate — Cổng chất lượng SonarQube làm rào chặn merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Với mọi pull request nhắm vào một nhánh được bảo vệ, pipeline PHẢI thực thi các chặng build, unit test, integration test, contract test và cổng chất lượng SonarQube, đúng theo thứ tự đó.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:109</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Pipeline PHẢI dừng lại trước chặng SonarQube nếu bất kỳ chặng trước đó (build, unit test, integration test, contract test) thất bại, và PHẢI báo chặng bị lỗi đó là lý do chặn ngay trên PR.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:112</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Hệ thống PHẢI báo một trạng thái cổng chất lượng duy nhất (đạt/không đạt) cho mỗi commit đầu (head commit) của PR, suy ra từ cấu hình cổng chất lượng SonarQube hiện hành (ngưỡng độ bao phủ, ngưỡng trùng lặp mã, các quy tắc về lỗi blocker/critical mới).</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Hệ thống PHẢI chặn việc merge mọi PR có trạng thái cổng chất lượng không đạt, bất kể vai trò hay mức quyền của người thực hiện merge, và KHÔNG ĐƯỢC cung cấp bất kỳ cơ chế ghi đè, đi vòng hay nút "cứ merge" nào cho một cổng đang không đạt.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Việc merge PHẢI được kiểm soát bằng branch protection của GitHub trên các nhánh được bảo vệ, với cổng chất lượng SonarQube (cùng các chặng build/unit/integration/contract đứng trước) được cấu hình là các required status check, và bật tùy chọn "Do not allow bypassing the above settings" để ngay cả quản trị viên repository cũng không thể merge vượt qua một check đang lỗi hoặc đang chờ. Nếu GitHub từng để lộ một đường ghi đè còn sót nằm ngoài thiết lập này, mọi lần ghi đè như vậy PHẢI được ghi lại trong nhật ký kiểm toán, gồm người thực hiện, PR, mốc thời gian và lý do đã nêu.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:121</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Khi cổng chất lượng đạt, hệ thống PHẢI hiển thị tỷ lệ phần trăm độ bao phủ, tỷ lệ phần trăm trùng lặp mã và số lượng code smell mới của phần thay đổi được phân tích, ngay trên chính PR (không bắt người dùng phải chuyển sang một dashboard SonarQube riêng mới xem được phần tóm tắt).</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:127</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Hệ thống PHẢI tự động chạy lại toàn bộ chuỗi chặng mỗi khi có commit mới được đẩy lên một PR đang được đánh giá, và PHẢI cập nhật trạng thái chặn merge của PR theo lượt chạy mới nhất chứ không theo lượt chạy trước đó.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Hệ thống PHẢI coi việc không kết nối được hoặc không hoàn tất được phân tích SonarQube (quá thời gian chờ, lỗi dịch vụ) là kết quả không đạt/bị chặn, chứ không phải là một check bị bỏ qua hay đã đạt.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:133</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>FR-009</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Các ngưỡng và quy tắc của cổng chất lượng PHẢI được định nghĩa trong một quality profile/quality gate SonarQube duy nhất được quản lý tập trung, thay vì cấu hình riêng theo từng repository, từng PR hay từng lập trình viên.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:135</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>FR-010</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Hệ thống PHẢI lưu giữ hồ sơ kết quả pipeline theo từng chặng và kết quả cổng chất lượng của mỗi PR, ít nhất trong suốt thời gian PR còn mở, phục vụ mục đích kiểm toán và xử lý sự cố.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:138</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một PR được mở nhắm vào nhánh được bảo vệ, Khi pipeline chạy, Thì nó thực thi build → unit test → integration test → contract test → cổng chất lượng SonarQube đúng theo trình tự đó, và trạng thái đạt/không đạt của từng chặng đều nhìn thấy được trên PR.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện cổng chất lượng SonarQube không đạt (độ bao phủ dưới ngưỡng, có lỗi blocker/critical mới, hoặc trùng lặp mã vượt mức), Khi có người cố merge PR, Thì thao tác merge bị chặn và không vai trò nào có sẵn cơ chế ghi đè để merge.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB3</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một chặng trước đó (build, unit test, integration test hoặc contract test) thất bại, Khi pipeline chạy tiếp, Thì chặng SonarQube không chạy và PR bị chặn tại chặng đã lỗi, với chặng đó được chỉ rõ là nguyên nhân.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện cổng chất lượng SonarQube đạt, Khi người soát xét xem trạng thái của PR, Thì độ bao phủ, mức trùng lặp và số lượng code smell của phần mã đã thay đổi đều nhìn thấy được trực tiếp trên PR.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB2</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện cổng chất lượng đã chạy ít nhất một lần cho một PR, Khi có commit mới được đẩy lên, Thì các chỉ số hiển thị được cập nhật theo lượt phân tích mới nhất chứ không phải theo lượt chạy đã cũ.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một PR đang bị chặn do cổng chất lượng không đạt, Khi lập trình viên đẩy lên một commit xử lý được vấn đề gốc, Thì toàn bộ chuỗi pipeline tự động chạy lại và trạng thái merge của PR được cập nhật ngay khi lượt phân tích mới hoàn tất.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:79</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB2</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện lượt chạy lại vượt qua cổng chất lượng, Khi lập trình viên kiểm tra PR, Thì rào chặn merge được gỡ bỏ mà không cần thêm bước phê duyệt thủ công nào ngoài chính sách soát xét sẵn có.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:82</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>100% các PR được mở nhắm vào nhánh được bảo vệ đều hiển thị một trạng thái cổng chất lượng đạt/không đạt duy nhất, suy ra từ trọn chuỗi build → unit → integration → contract → SonarQube, trước khi được phép merge.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:158</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SC-002</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Có 0 PR với cổng chất lượng không đạt được merge vào nhánh được bảo vệ, xét trên mọi vai trò, trong bất kỳ chu kỳ kiểm toán 90 ngày nào.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:161</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SC-003</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Người soát xét nhìn thấy được độ bao phủ, mức trùng lặp và số lượng code smell trực tiếp trên một PR đã đạt cổng chất lượng mà không phải rời khỏi màn hình PR, với 100% số PR đã merge.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:163</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SC-004</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Một PR chỉ bị chặn vì sụt giảm độ bao phủ/chất lượng sẽ merge được sau đúng một lượt chạy pipeline (không cần can thiệp thủ công), kể từ khi vấn đề mã nguồn gốc rễ được sửa và đẩy lên.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:165</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SC-005</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Mọi nỗ lực đi vòng hay ghi đè trên một PR đang bị chặn hoặc là bất khả thi về mặt kỹ thuật, hoặc tạo ra một bản ghi kiểm toán ngay trong cùng lượt chạy pipeline, đạt 100% số lần.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>specs/012-sonarqube-quality-gate/spec.md:167</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E22"/>
+  <mergeCells count="3">
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8504,4 +11840,782 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>008-versioned-event-schemas — Schema sự kiện có đánh phiên bản — OrderPlaced, BasketCheckedOut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Cấp</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Schema có đánh phiên bản của OrderPlaced và BasketCheckedOut PHẢI được định nghĩa tại một vị trí hợp đồng (contracts) dùng chung, chứ không nằm trực tiếp trong service phát ra chúng.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:108</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Mỗi phiên bản schema sự kiện PHẢI mang một định danh phiên bản tường minh, không gây nhập nhằng, để bên phát và bên tiêu thụ dùng nó phân biệt với các phiên bản khác của cùng sự kiện.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:110</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Một thay đổi phá vỡ tương thích trên schema sự kiện đã công bố (thêm trường bắt buộc, bỏ trường, đổi kiểu dữ liệu/ngữ nghĩa của trường) PHẢI được phát hành dưới dạng một phiên bản mới tường minh, thay vì sửa đổi trực tiếp phiên bản hiện có.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:112</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Khi một phiên bản mới của schema sự kiện được đưa ra để thay thế một thay đổi phá vỡ tương thích, phiên bản trước đó PHẢI vẫn được định nghĩa và vẫn hoạt động trong suốt một khung thời gian ngưng dùng (deprecation window) đã ghi trong tài liệu.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Khung thời gian ngưng dùng và các điều kiện để được phép gỡ bỏ một phiên bản schema đã bị thay thế PHẢI được ghi thành tài liệu ngay cạnh chính schema đó.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:117</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>PHẢI có một bước kiểm tra tính tương thích để kiểm chứng các thay đổi schema của OrderPlaced và BasketCheckedOut, và bước này PHẢI báo lỗi khi một thay đổi phá vỡ tương thích được thực hiện mà không kèm phiên bản mới tương ứng.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Các bên tiêu thụ OrderPlaced và BasketCheckedOut KHÔNG ĐƯỢC lỗi khi giải mã (deserialization) trong trường hợp một thể hiện sự kiện chứa những trường không có trong hiểu biết schema của bên tiêu thụ đó.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:122</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Mỗi schema sự kiện PHẢI có tài liệu mô tả các trường của nó, trường nào bắt buộc và trường nào tùy chọn, cùng lịch sử phiên bản, ở dạng tìm thấy được từ vị trí hợp đồng dùng chung.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:124</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>FR-009</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Một sự kiện OrderPlaced do service phát hành tạo ra PHẢI kiểm chứng hợp lệ thành công so với schema đã công bố của nó.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:126</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có liên kết tường minh trong spec</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Không có trong spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện xét schema sự kiện OrderPlaced hoặc BasketCheckedOut, Khi lập trình viên tìm nơi nó được định nghĩa, Thì nó nằm ở vị trí hợp đồng dùng chung, chứ không nằm trực tiếp trong service phát hành.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>US1-KB2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một service phát hành phát ra OrderPlaced hoặc BasketCheckedOut, Khi soát xét mã nguồn của service đó, Thì nó tham chiếu tới định nghĩa schema dùng chung chứ không sao chép lặp lại định nghĩa trường/kiểu dữ liệu ở nội bộ.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một thay đổi schema của OrderPlaced hoặc BasketCheckedOut là phá vỡ tương thích (ví dụ thêm trường bắt buộc, bỏ trường, hoặc đổi kiểu dữ liệu của trường), Khi thay đổi đó được phát hành, Thì nó mang một phiên bản mới tường minh và phiên bản trước vẫn tiếp tục hoạt động trong khung thời gian ngưng dùng đã ghi trong tài liệu.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện lập trình viên thêm một trường bắt buộc mới vào schema mà không đưa ra phiên bản mới, Khi thay đổi được kiểm chứng, Thì bước kiểm tra tính tương thích báo lỗi và chặn thay đổi đó.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:61</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>US2-KB3</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một phiên bản schema đã bị thay thế và đang nằm trong khung thời gian ngưng dùng, Khi một bên tiêu thụ vẫn được xây dựng theo phiên bản đó xử lý một sự kiện, Thì nó tiếp tục hoạt động đúng như tài liệu mô tả.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:63</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một bên tiêu thụ nhận được sự kiện OrderPlaced hoặc BasketCheckedOut chứa các trường mà bên tiêu thụ đó không biết, Khi sự kiện được giải mã, Thì việc giải mã không thất bại và các trường mà bên tiêu thụ nhận biết được vẫn dùng được bình thường.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>US3-KB2</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Kịch bản chấp nhận</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Với điều kiện một sự kiện OrderPlaced được phát hành và được kiểm chứng, Khi đối chiếu nó với schema đã công bố của nó, Thì nó kiểm chứng hợp lệ thành công.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được chưa gắn với FR nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SC-001</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>100% các định nghĩa schema của OrderPlaced và BasketCheckedOut nằm tại vị trí hợp đồng dùng chung, không còn định nghĩa schema nội tuyến/trùng lặp nào sót lại trong các service phát hành.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:145</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SC-002</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Một thay đổi phá vỡ tương thích đưa vào OrderPlaced hoặc BasketCheckedOut mà không kèm phiên bản mới đều bị bước kiểm tra tính tương thích bắt được trước khi merge, ở 100% số trường hợp đã kiểm thử.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:148</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SC-003</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Một bên tiêu thụ được xây dựng theo phiên bản schema cũ vẫn xử lý thành công một phiên bản mới hơn chỉ bổ sung thêm trường của cùng sự kiện, không có lỗi giải mã nào, trên mọi kịch bản đã kiểm thử.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:150</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SC-004</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả đo lường được</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Lập trình viên có thể tìm được phiên bản hiện hành, các phiên bản cũ còn được hỗ trợ, và khung thời gian ngưng dùng của OrderPlaced hoặc BasketCheckedOut hoàn toàn từ vị trí hợp đồng dùng chung, không phải đọc mã nguồn của service khác.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>specs/008-versioned-event-schemas/spec.md:153</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E20"/>
+  <mergeCells count="3">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A31:E31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>